--- a/backend/data/financials_by_company/0092.HK.xlsx
+++ b/backend/data/financials_by_company/0092.HK.xlsx
@@ -662,578 +662,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-6807.921102</v>
+        <v>-2569545</v>
       </c>
       <c r="C2" t="n">
-        <v>0.043363</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-12365000</v>
+        <v>-4194000</v>
       </c>
       <c r="E2" t="n">
-        <v>-157000</v>
+        <v>-15573000</v>
       </c>
       <c r="F2" t="n">
-        <v>-157000</v>
+        <v>-15573000</v>
       </c>
       <c r="G2" t="n">
-        <v>-12420000</v>
+        <v>-70852000</v>
       </c>
       <c r="H2" t="n">
-        <v>214000</v>
+        <v>13327000</v>
       </c>
       <c r="I2" t="n">
-        <v>197212000</v>
+        <v>91676000</v>
       </c>
       <c r="J2" t="n">
-        <v>-12522000</v>
+        <v>-19767000</v>
       </c>
       <c r="K2" t="n">
-        <v>-12736000</v>
+        <v>-33094000</v>
       </c>
       <c r="L2" t="n">
-        <v>715000</v>
+        <v>-30426000</v>
       </c>
       <c r="M2" t="n">
-        <v>40000</v>
+        <v>32354000</v>
       </c>
       <c r="N2" t="n">
-        <v>755000</v>
+        <v>1928000</v>
       </c>
       <c r="O2" t="n">
-        <v>-12269807.921102</v>
+        <v>-57848545</v>
       </c>
       <c r="P2" t="n">
-        <v>-12420000</v>
+        <v>-59822000</v>
       </c>
       <c r="Q2" t="n">
-        <v>219904000</v>
+        <v>122183000</v>
       </c>
       <c r="R2" t="n">
-        <v>683831000</v>
+        <v>197695250</v>
       </c>
       <c r="S2" t="n">
-        <v>683831000</v>
+        <v>197695250</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0182</v>
+        <v>-0.3024</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0182</v>
+        <v>-0.3024</v>
       </c>
       <c r="V2" t="n">
-        <v>-12420000</v>
+        <v>-59822000</v>
       </c>
       <c r="W2" t="n">
-        <v>-12420000</v>
+        <v>-59822000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-12420000</v>
+        <v>-59822000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-198000</v>
+        <v>-2880000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-12222000</v>
+        <v>-56942000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>11030000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-12222000</v>
+        <v>-67972000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-554000</v>
+        <v>2524000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-12776000</v>
+        <v>-65448000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1556000</v>
+        <v>1231000</v>
       </c>
       <c r="AG2" t="n">
-        <v>19328000</v>
+        <v>-997000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-32136000</v>
+        <v>-7465000</v>
       </c>
       <c r="AI2" t="n">
-        <v>10468000</v>
+        <v>1080000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2340000</v>
+        <v>7382000</v>
       </c>
       <c r="AK2" t="n">
-        <v>715000</v>
+        <v>-30426000</v>
       </c>
       <c r="AL2" t="n">
-        <v>40000</v>
+        <v>32354000</v>
       </c>
       <c r="AM2" t="n">
-        <v>755000</v>
+        <v>1928000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-11292000</v>
+        <v>-23779000</v>
       </c>
       <c r="AO2" t="n">
-        <v>22692000</v>
+        <v>30507000</v>
       </c>
       <c r="AP2" t="n">
-        <v>22692000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>30507000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>25685000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>22692000</v>
+        <v>30507000</v>
       </c>
       <c r="AS2" t="n">
-        <v>11400000</v>
+        <v>6728000</v>
       </c>
       <c r="AT2" t="n">
-        <v>197212000</v>
+        <v>91676000</v>
       </c>
       <c r="AU2" t="n">
-        <v>208612000</v>
+        <v>98404000</v>
       </c>
       <c r="AV2" t="n">
-        <v>208612000</v>
+        <v>98404000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>301125</v>
+        <v>-3168330</v>
       </c>
       <c r="C3" t="n">
         <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>-12773000</v>
+        <v>-15588000</v>
       </c>
       <c r="E3" t="n">
-        <v>1825000</v>
+        <v>-19202000</v>
       </c>
       <c r="F3" t="n">
-        <v>1825000</v>
+        <v>-19202000</v>
       </c>
       <c r="G3" t="n">
-        <v>-12731000</v>
+        <v>-53747000</v>
       </c>
       <c r="H3" t="n">
-        <v>555000</v>
+        <v>5873000</v>
       </c>
       <c r="I3" t="n">
-        <v>21242000</v>
+        <v>57734000</v>
       </c>
       <c r="J3" t="n">
-        <v>-10948000</v>
+        <v>-34790000</v>
       </c>
       <c r="K3" t="n">
-        <v>-11503000</v>
+        <v>-40663000</v>
       </c>
       <c r="L3" t="n">
-        <v>2527000</v>
+        <v>-9696000</v>
       </c>
       <c r="M3" t="n">
-        <v>172000</v>
+        <v>11947000</v>
       </c>
       <c r="N3" t="n">
-        <v>2699000</v>
+        <v>2251000</v>
       </c>
       <c r="O3" t="n">
-        <v>-14254875</v>
+        <v>-37713330</v>
       </c>
       <c r="P3" t="n">
-        <v>-12183000</v>
+        <v>-50869000</v>
       </c>
       <c r="Q3" t="n">
-        <v>40660000</v>
+        <v>84501000</v>
       </c>
       <c r="R3" t="n">
-        <v>683830750</v>
+        <v>462739000</v>
       </c>
       <c r="S3" t="n">
-        <v>683830750</v>
+        <v>462739000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.018</v>
+        <v>-0.11</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.018</v>
+        <v>-0.11</v>
       </c>
       <c r="V3" t="n">
-        <v>-12183000</v>
+        <v>-50869000</v>
       </c>
       <c r="W3" t="n">
-        <v>-12183000</v>
+        <v>-50869000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-12183000</v>
+        <v>-50869000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-459000</v>
+        <v>-709000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-11724000</v>
+        <v>-50160000</v>
       </c>
       <c r="AB3" t="n">
-        <v>548000</v>
+        <v>2878000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-12272000</v>
+        <v>-53038000</v>
       </c>
       <c r="AD3" t="n">
-        <v>597000</v>
+        <v>428000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11675000</v>
+        <v>-52610000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1092000</v>
+        <v>1393000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-7527000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-5339000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1384000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>7527000</v>
+        <v>200000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3755000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2527000</v>
+        <v>-9696000</v>
       </c>
       <c r="AL3" t="n">
-        <v>172000</v>
+        <v>11947000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2699000</v>
+        <v>2251000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-15368000</v>
+        <v>-23532000</v>
       </c>
       <c r="AO3" t="n">
-        <v>19418000</v>
+        <v>26767000</v>
       </c>
       <c r="AP3" t="n">
-        <v>19418000</v>
+        <v>26767000</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>19418000</v>
+        <v>26767000</v>
       </c>
       <c r="AS3" t="n">
-        <v>4050000</v>
+        <v>3235000</v>
       </c>
       <c r="AT3" t="n">
-        <v>21242000</v>
+        <v>57734000</v>
       </c>
       <c r="AU3" t="n">
-        <v>25292000</v>
+        <v>60969000</v>
       </c>
       <c r="AV3" t="n">
-        <v>25292000</v>
+        <v>60969000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-3168330</v>
+        <v>301125</v>
       </c>
       <c r="C4" t="n">
         <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>-15588000</v>
+        <v>-12773000</v>
       </c>
       <c r="E4" t="n">
-        <v>-19202000</v>
+        <v>1825000</v>
       </c>
       <c r="F4" t="n">
-        <v>-19202000</v>
+        <v>1825000</v>
       </c>
       <c r="G4" t="n">
-        <v>-53747000</v>
+        <v>-12731000</v>
       </c>
       <c r="H4" t="n">
-        <v>5873000</v>
+        <v>555000</v>
       </c>
       <c r="I4" t="n">
-        <v>57734000</v>
+        <v>21242000</v>
       </c>
       <c r="J4" t="n">
-        <v>-34790000</v>
+        <v>-10948000</v>
       </c>
       <c r="K4" t="n">
-        <v>-40663000</v>
+        <v>-11503000</v>
       </c>
       <c r="L4" t="n">
-        <v>-9696000</v>
+        <v>2527000</v>
       </c>
       <c r="M4" t="n">
-        <v>11947000</v>
+        <v>172000</v>
       </c>
       <c r="N4" t="n">
-        <v>2251000</v>
+        <v>2699000</v>
       </c>
       <c r="O4" t="n">
-        <v>-37713330</v>
+        <v>-14254875</v>
       </c>
       <c r="P4" t="n">
-        <v>-50869000</v>
+        <v>-12183000</v>
       </c>
       <c r="Q4" t="n">
-        <v>84501000</v>
+        <v>40660000</v>
       </c>
       <c r="R4" t="n">
-        <v>462739000</v>
+        <v>683830750</v>
       </c>
       <c r="S4" t="n">
-        <v>462739000</v>
+        <v>683830750</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.11</v>
+        <v>-0.018</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.11</v>
+        <v>-0.018</v>
       </c>
       <c r="V4" t="n">
-        <v>-50869000</v>
+        <v>-12183000</v>
       </c>
       <c r="W4" t="n">
-        <v>-50869000</v>
+        <v>-12183000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-50869000</v>
+        <v>-12183000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-709000</v>
+        <v>-459000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-50160000</v>
+        <v>-11724000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2878000</v>
+        <v>548000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-53038000</v>
+        <v>-12272000</v>
       </c>
       <c r="AD4" t="n">
-        <v>428000</v>
+        <v>597000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-52610000</v>
+        <v>-11675000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1393000</v>
+        <v>1092000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5339000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1384000</v>
-      </c>
+        <v>-7527000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>200000</v>
+        <v>7527000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3755000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-9696000</v>
+        <v>2527000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11947000</v>
+        <v>172000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2251000</v>
+        <v>2699000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-23532000</v>
+        <v>-15368000</v>
       </c>
       <c r="AO4" t="n">
-        <v>26767000</v>
+        <v>19418000</v>
       </c>
       <c r="AP4" t="n">
-        <v>26767000</v>
+        <v>19418000</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>26767000</v>
+        <v>19418000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3235000</v>
+        <v>4050000</v>
       </c>
       <c r="AT4" t="n">
-        <v>57734000</v>
+        <v>21242000</v>
       </c>
       <c r="AU4" t="n">
-        <v>60969000</v>
+        <v>25292000</v>
       </c>
       <c r="AV4" t="n">
-        <v>60969000</v>
+        <v>25292000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-2569545</v>
+        <v>-6807.921102</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.043363</v>
       </c>
       <c r="D5" t="n">
-        <v>-4194000</v>
+        <v>-12365000</v>
       </c>
       <c r="E5" t="n">
-        <v>-15573000</v>
+        <v>-157000</v>
       </c>
       <c r="F5" t="n">
-        <v>-15573000</v>
+        <v>-157000</v>
       </c>
       <c r="G5" t="n">
-        <v>-70852000</v>
+        <v>-12420000</v>
       </c>
       <c r="H5" t="n">
-        <v>13327000</v>
+        <v>214000</v>
       </c>
       <c r="I5" t="n">
-        <v>91676000</v>
+        <v>197212000</v>
       </c>
       <c r="J5" t="n">
-        <v>-19767000</v>
+        <v>-12522000</v>
       </c>
       <c r="K5" t="n">
-        <v>-33094000</v>
+        <v>-12736000</v>
       </c>
       <c r="L5" t="n">
-        <v>-30426000</v>
+        <v>715000</v>
       </c>
       <c r="M5" t="n">
-        <v>32354000</v>
+        <v>40000</v>
       </c>
       <c r="N5" t="n">
-        <v>1928000</v>
+        <v>755000</v>
       </c>
       <c r="O5" t="n">
-        <v>-57848545</v>
+        <v>-12269807.921102</v>
       </c>
       <c r="P5" t="n">
-        <v>-59822000</v>
+        <v>-12420000</v>
       </c>
       <c r="Q5" t="n">
-        <v>122183000</v>
+        <v>219904000</v>
       </c>
       <c r="R5" t="n">
-        <v>197695250</v>
+        <v>683831000</v>
       </c>
       <c r="S5" t="n">
-        <v>197695250</v>
+        <v>683831000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3024</v>
+        <v>-0.0182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3024</v>
+        <v>-0.0182</v>
       </c>
       <c r="V5" t="n">
-        <v>-59822000</v>
+        <v>-12420000</v>
       </c>
       <c r="W5" t="n">
-        <v>-59822000</v>
+        <v>-12420000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-59822000</v>
+        <v>-12420000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2880000</v>
+        <v>-198000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-56942000</v>
+        <v>-12222000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11030000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-67972000</v>
+        <v>-12222000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2524000</v>
+        <v>-554000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-65448000</v>
+        <v>-12776000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1231000</v>
+        <v>1556000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-997000</v>
+        <v>19328000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-7465000</v>
+        <v>-32136000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1080000</v>
+        <v>10468000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7382000</v>
+        <v>2340000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-30426000</v>
+        <v>715000</v>
       </c>
       <c r="AL5" t="n">
-        <v>32354000</v>
+        <v>40000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1928000</v>
+        <v>755000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-23779000</v>
+        <v>-11292000</v>
       </c>
       <c r="AO5" t="n">
-        <v>30507000</v>
+        <v>22692000</v>
       </c>
       <c r="AP5" t="n">
-        <v>30507000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>25685000</v>
-      </c>
+        <v>22692000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>30507000</v>
+        <v>22692000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6728000</v>
+        <v>11400000</v>
       </c>
       <c r="AT5" t="n">
-        <v>91676000</v>
+        <v>197212000</v>
       </c>
       <c r="AU5" t="n">
-        <v>98404000</v>
+        <v>208612000</v>
       </c>
       <c r="AV5" t="n">
-        <v>98404000</v>
+        <v>208612000</v>
       </c>
     </row>
   </sheetData>
@@ -1579,108 +1579,118 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>683831000</v>
+        <v>197695200</v>
       </c>
       <c r="C2" t="n">
-        <v>683831000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>197695200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>110458000</v>
+      </c>
       <c r="E2" t="n">
-        <v>1894000</v>
+        <v>229352000</v>
       </c>
       <c r="F2" t="n">
-        <v>96494000</v>
+        <v>-6967000</v>
       </c>
       <c r="G2" t="n">
-        <v>96494000</v>
+        <v>216339000</v>
       </c>
       <c r="H2" t="n">
-        <v>62186000</v>
+        <v>184140000</v>
       </c>
       <c r="I2" t="n">
-        <v>96494000</v>
+        <v>-6967000</v>
       </c>
       <c r="J2" t="n">
-        <v>1894000</v>
+        <v>6046000</v>
       </c>
       <c r="K2" t="n">
-        <v>96494000</v>
+        <v>-6967000</v>
       </c>
       <c r="L2" t="n">
-        <v>96494000</v>
+        <v>216339000</v>
       </c>
       <c r="M2" t="n">
-        <v>96469000</v>
+        <v>64095000</v>
       </c>
       <c r="N2" t="n">
-        <v>-25000</v>
+        <v>71062000</v>
       </c>
       <c r="O2" t="n">
-        <v>96494000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-4609925000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2235182000</v>
-      </c>
+        <v>-6967000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>6838000</v>
+        <v>68383000</v>
       </c>
       <c r="S2" t="n">
-        <v>6838000</v>
+        <v>68383000</v>
       </c>
       <c r="T2" t="n">
-        <v>165920000</v>
+        <v>350797000</v>
       </c>
       <c r="U2" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>250893000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>16018000</v>
+      </c>
       <c r="W2" t="n">
-        <v>7175000</v>
+        <v>9616000</v>
       </c>
       <c r="X2" t="n">
-        <v>925000</v>
+        <v>225259000</v>
       </c>
       <c r="Y2" t="n">
-        <v>925000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>1953000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>223306000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>157820000</v>
+        <v>99904000</v>
       </c>
       <c r="AB2" t="n">
-        <v>969000</v>
+        <v>4093000</v>
       </c>
       <c r="AC2" t="n">
-        <v>969000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>4093000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1062000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>152109000</v>
+        <v>66094000</v>
       </c>
       <c r="AG2" t="n">
-        <v>64475000</v>
+        <v>43528000</v>
       </c>
       <c r="AH2" t="n">
-        <v>864000</v>
+        <v>2095000</v>
       </c>
       <c r="AI2" t="n">
-        <v>86770000</v>
+        <v>20471000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>262389000</v>
+        <v>414892000</v>
       </c>
       <c r="AK2" t="n">
-        <v>42383000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+        <v>130848000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
         <v>2000</v>
       </c>
@@ -1688,74 +1698,82 @@
         <v>2000</v>
       </c>
       <c r="AP2" t="n">
-        <v>34262000</v>
+        <v>50022000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8119000</v>
+        <v>42402000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-12405000</v>
+        <v>-263941000</v>
       </c>
       <c r="AS2" t="n">
-        <v>20524000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1074000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>306343000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>1581000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>19450000</v>
+        <v>289159000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>1581000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>15603000</v>
+      </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>220006000</v>
+        <v>284044000</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>22719000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>7407000</v>
+        <v>38564000</v>
       </c>
       <c r="BD2" t="n">
-        <v>3574000</v>
+        <v>24186000</v>
       </c>
       <c r="BE2" t="n">
-        <v>720000</v>
+        <v>6581000</v>
       </c>
       <c r="BF2" t="n">
-        <v>3113000</v>
+        <v>7797000</v>
       </c>
       <c r="BG2" t="n">
-        <v>6624000</v>
+        <v>22773000</v>
       </c>
       <c r="BH2" t="n">
-        <v>184000</v>
+        <v>285000</v>
       </c>
       <c r="BI2" t="n">
-        <v>180671000</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
+        <v>40409000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-1122000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>41531000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>25120000</v>
+        <v>154741000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10421000</v>
+        <v>41893000</v>
       </c>
       <c r="BN2" t="n">
-        <v>14699000</v>
+        <v>112848000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>683831000</v>
@@ -1765,40 +1783,40 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>840000</v>
+        <v>1800000</v>
       </c>
       <c r="F3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="G3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="H3" t="n">
-        <v>94071000</v>
+        <v>77939000</v>
       </c>
       <c r="I3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="J3" t="n">
-        <v>840000</v>
+        <v>1800000</v>
       </c>
       <c r="K3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="L3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="M3" t="n">
-        <v>128498000</v>
+        <v>149619000</v>
       </c>
       <c r="N3" t="n">
-        <v>17246000</v>
+        <v>18764000</v>
       </c>
       <c r="O3" t="n">
-        <v>111252000</v>
+        <v>130855000</v>
       </c>
       <c r="P3" t="n">
-        <v>-4597505000</v>
+        <v>-4585322000</v>
       </c>
       <c r="Q3" t="n">
         <v>2214667000</v>
@@ -1810,53 +1828,61 @@
         <v>27353000</v>
       </c>
       <c r="T3" t="n">
-        <v>45532000</v>
+        <v>29426000</v>
       </c>
       <c r="U3" t="n">
-        <v>8049000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>9865000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" t="n">
-        <v>8049000</v>
+        <v>9025000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>840000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>840000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>37483000</v>
+        <v>19561000</v>
       </c>
       <c r="AB3" t="n">
-        <v>840000</v>
+        <v>960000</v>
       </c>
       <c r="AC3" t="n">
-        <v>840000</v>
+        <v>960000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>27132000</v>
+        <v>12688000</v>
       </c>
       <c r="AG3" t="n">
-        <v>21315000</v>
+        <v>8934000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1257000</v>
+        <v>2759000</v>
       </c>
       <c r="AI3" t="n">
-        <v>4560000</v>
+        <v>995000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174030000</v>
+        <v>179045000</v>
       </c>
       <c r="AK3" t="n">
-        <v>42476000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+        <v>81545000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
       <c r="AN3" t="n">
         <v>2000</v>
       </c>
@@ -1864,25 +1890,23 @@
         <v>2000</v>
       </c>
       <c r="AP3" t="n">
-        <v>37959000</v>
+        <v>47275000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4515000</v>
+        <v>371000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-13991000</v>
+        <v>-14033000</v>
       </c>
       <c r="AS3" t="n">
-        <v>18506000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
+        <v>14404000</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>4515000</v>
+        <v>371000</v>
       </c>
       <c r="AV3" t="n">
-        <v>18506000</v>
+        <v>14404000</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1894,52 +1918,52 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>131554000</v>
+        <v>97500000</v>
       </c>
       <c r="BA3" t="n">
-        <v>37610000</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>7335000</v>
+        <v>12882000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3441000</v>
+        <v>8118000</v>
       </c>
       <c r="BE3" t="n">
-        <v>223000</v>
+        <v>2169000</v>
       </c>
       <c r="BF3" t="n">
-        <v>3671000</v>
+        <v>2595000</v>
       </c>
       <c r="BG3" t="n">
-        <v>35216000</v>
+        <v>23953000</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>8023000</v>
+        <v>10016000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-346000</v>
+        <v>-255000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8369000</v>
+        <v>10271000</v>
       </c>
       <c r="BL3" t="n">
-        <v>43370000</v>
+        <v>46478000</v>
       </c>
       <c r="BM3" t="n">
-        <v>34223000</v>
+        <v>21985000</v>
       </c>
       <c r="BN3" t="n">
-        <v>9147000</v>
+        <v>24493000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>683831000</v>
@@ -1949,40 +1973,40 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1800000</v>
+        <v>840000</v>
       </c>
       <c r="F4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="G4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="H4" t="n">
-        <v>77939000</v>
+        <v>94071000</v>
       </c>
       <c r="I4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="J4" t="n">
-        <v>1800000</v>
+        <v>840000</v>
       </c>
       <c r="K4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="L4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="M4" t="n">
-        <v>149619000</v>
+        <v>128498000</v>
       </c>
       <c r="N4" t="n">
-        <v>18764000</v>
+        <v>17246000</v>
       </c>
       <c r="O4" t="n">
-        <v>130855000</v>
+        <v>111252000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4585322000</v>
+        <v>-4597505000</v>
       </c>
       <c r="Q4" t="n">
         <v>2214667000</v>
@@ -1994,61 +2018,53 @@
         <v>27353000</v>
       </c>
       <c r="T4" t="n">
-        <v>29426000</v>
+        <v>45532000</v>
       </c>
       <c r="U4" t="n">
-        <v>9865000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
+        <v>8049000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>9025000</v>
+        <v>8049000</v>
       </c>
       <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>37483000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>840000</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>840000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>19561000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>960000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>960000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>12688000</v>
+        <v>27132000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8934000</v>
+        <v>21315000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2759000</v>
+        <v>1257000</v>
       </c>
       <c r="AI4" t="n">
-        <v>995000</v>
+        <v>4560000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>179045000</v>
+        <v>174030000</v>
       </c>
       <c r="AK4" t="n">
-        <v>81545000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
+        <v>42476000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
         <v>2000</v>
       </c>
@@ -2056,23 +2072,25 @@
         <v>2000</v>
       </c>
       <c r="AP4" t="n">
-        <v>47275000</v>
+        <v>37959000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>371000</v>
+        <v>4515000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-14033000</v>
+        <v>-13991000</v>
       </c>
       <c r="AS4" t="n">
-        <v>14404000</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+        <v>18506000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
       <c r="AU4" t="n">
-        <v>371000</v>
+        <v>4515000</v>
       </c>
       <c r="AV4" t="n">
-        <v>14404000</v>
+        <v>18506000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -2084,163 +2102,153 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>97500000</v>
+        <v>131554000</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>37610000</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>12882000</v>
+        <v>7335000</v>
       </c>
       <c r="BD4" t="n">
-        <v>8118000</v>
+        <v>3441000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2169000</v>
+        <v>223000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2595000</v>
+        <v>3671000</v>
       </c>
       <c r="BG4" t="n">
-        <v>23953000</v>
+        <v>35216000</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>10016000</v>
+        <v>8023000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-255000</v>
+        <v>-346000</v>
       </c>
       <c r="BK4" t="n">
-        <v>10271000</v>
+        <v>8369000</v>
       </c>
       <c r="BL4" t="n">
-        <v>46478000</v>
+        <v>43370000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21985000</v>
+        <v>34223000</v>
       </c>
       <c r="BN4" t="n">
-        <v>24493000</v>
+        <v>9147000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>197695200</v>
+        <v>683831000</v>
       </c>
       <c r="C5" t="n">
-        <v>197695200</v>
-      </c>
-      <c r="D5" t="n">
-        <v>110458000</v>
-      </c>
+        <v>683831000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>229352000</v>
+        <v>1894000</v>
       </c>
       <c r="F5" t="n">
-        <v>-6967000</v>
+        <v>96494000</v>
       </c>
       <c r="G5" t="n">
-        <v>216339000</v>
+        <v>96494000</v>
       </c>
       <c r="H5" t="n">
-        <v>184140000</v>
+        <v>62186000</v>
       </c>
       <c r="I5" t="n">
-        <v>-6967000</v>
+        <v>96494000</v>
       </c>
       <c r="J5" t="n">
-        <v>6046000</v>
+        <v>1894000</v>
       </c>
       <c r="K5" t="n">
-        <v>-6967000</v>
+        <v>96494000</v>
       </c>
       <c r="L5" t="n">
-        <v>216339000</v>
+        <v>96494000</v>
       </c>
       <c r="M5" t="n">
-        <v>64095000</v>
+        <v>96469000</v>
       </c>
       <c r="N5" t="n">
-        <v>71062000</v>
+        <v>-25000</v>
       </c>
       <c r="O5" t="n">
-        <v>-6967000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>96494000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4609925000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2235182000</v>
+      </c>
       <c r="R5" t="n">
-        <v>68383000</v>
+        <v>6838000</v>
       </c>
       <c r="S5" t="n">
-        <v>68383000</v>
+        <v>6838000</v>
       </c>
       <c r="T5" t="n">
-        <v>350797000</v>
+        <v>165920000</v>
       </c>
       <c r="U5" t="n">
-        <v>250893000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>16018000</v>
-      </c>
+        <v>8100000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>9616000</v>
+        <v>7175000</v>
       </c>
       <c r="X5" t="n">
-        <v>225259000</v>
+        <v>925000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1953000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>223306000</v>
-      </c>
+        <v>925000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>99904000</v>
+        <v>157820000</v>
       </c>
       <c r="AB5" t="n">
-        <v>4093000</v>
+        <v>969000</v>
       </c>
       <c r="AC5" t="n">
-        <v>4093000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1062000</v>
-      </c>
+        <v>969000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>66094000</v>
+        <v>152109000</v>
       </c>
       <c r="AG5" t="n">
-        <v>43528000</v>
+        <v>64475000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2095000</v>
+        <v>864000</v>
       </c>
       <c r="AI5" t="n">
-        <v>20471000</v>
+        <v>86770000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>414892000</v>
+        <v>262389000</v>
       </c>
       <c r="AK5" t="n">
-        <v>130848000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>42383000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
         <v>2000</v>
       </c>
@@ -2248,77 +2256,69 @@
         <v>2000</v>
       </c>
       <c r="AP5" t="n">
-        <v>50022000</v>
+        <v>34262000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>42402000</v>
+        <v>8119000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-263941000</v>
+        <v>-12405000</v>
       </c>
       <c r="AS5" t="n">
-        <v>306343000</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>1581000</v>
-      </c>
+        <v>20524000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>289159000</v>
+        <v>19450000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1581000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>15603000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>284044000</v>
+        <v>220006000</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
-      <c r="BB5" t="n">
-        <v>22719000</v>
-      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>38564000</v>
+        <v>7407000</v>
       </c>
       <c r="BD5" t="n">
-        <v>24186000</v>
+        <v>3574000</v>
       </c>
       <c r="BE5" t="n">
-        <v>6581000</v>
+        <v>720000</v>
       </c>
       <c r="BF5" t="n">
-        <v>7797000</v>
+        <v>3113000</v>
       </c>
       <c r="BG5" t="n">
-        <v>22773000</v>
+        <v>6624000</v>
       </c>
       <c r="BH5" t="n">
-        <v>285000</v>
+        <v>184000</v>
       </c>
       <c r="BI5" t="n">
-        <v>40409000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-1122000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>41531000</v>
-      </c>
+        <v>180671000</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>154741000</v>
+        <v>25120000</v>
       </c>
       <c r="BM5" t="n">
-        <v>41893000</v>
+        <v>10421000</v>
       </c>
       <c r="BN5" t="n">
-        <v>112848000</v>
+        <v>14699000</v>
       </c>
     </row>
   </sheetData>
@@ -2584,562 +2584,562 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-65870000</v>
+        <v>29156000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>-25000000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
-        <v>-4227000</v>
+        <v>-11554000</v>
       </c>
       <c r="G2" t="n">
-        <v>14699000</v>
+        <v>135567000</v>
       </c>
       <c r="H2" t="n">
-        <v>9150000</v>
+        <v>107051000</v>
       </c>
       <c r="I2" t="n">
-        <v>-460000</v>
+        <v>14583000</v>
       </c>
       <c r="J2" t="n">
-        <v>6009000</v>
+        <v>13933000</v>
       </c>
       <c r="K2" t="n">
-        <v>25040000</v>
+        <v>-56115000</v>
       </c>
       <c r="L2" t="n">
-        <v>25998000</v>
+        <v>8000</v>
       </c>
       <c r="M2" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-26242000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-25000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-25000000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
+        <v>-25000000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>42612000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2584000</v>
-      </c>
+        <v>29338000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>848000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4317000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4317000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>729000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>10230000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10230000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>45897000</v>
+        <v>19730000</v>
       </c>
       <c r="AC2" t="n">
-        <v>45897000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
+        <v>19730000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-4227000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-11354000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>200000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>-4227000</v>
+        <v>-11554000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-61643000</v>
+        <v>40710000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-880000</v>
+        <v>-1280000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-51176000</v>
+        <v>38205000</v>
       </c>
       <c r="AM2" t="n">
-        <v>130000</v>
+        <v>11928000</v>
       </c>
       <c r="AN2" t="n">
-        <v>99709000</v>
+        <v>9179000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-72000</v>
+        <v>-5073000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-150943000</v>
+        <v>22468000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-715000</v>
+        <v>21672000</v>
       </c>
       <c r="AR2" t="n">
-        <v>214000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
+        <v>13327000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>214000</v>
+        <v>13327000</v>
       </c>
       <c r="AU2" t="n">
-        <v>23018000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>12426000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-55000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>-32136000</v>
+        <v>726000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-12776000</v>
+        <v>-52753000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-3609000</v>
+        <v>-13249000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1478000</v>
+        <v>-226387000</v>
       </c>
       <c r="D3" t="n">
-        <v>3582000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>197897000</v>
       </c>
       <c r="F3" t="n">
-        <v>-5698000</v>
+        <v>-11002000</v>
       </c>
       <c r="G3" t="n">
-        <v>9150000</v>
+        <v>24493000</v>
       </c>
       <c r="H3" t="n">
-        <v>24493000</v>
+        <v>135567000</v>
       </c>
       <c r="I3" t="n">
-        <v>-3195000</v>
+        <v>-2697000</v>
       </c>
       <c r="J3" t="n">
-        <v>-12148000</v>
+        <v>-108377000</v>
       </c>
       <c r="K3" t="n">
-        <v>2863000</v>
+        <v>-48130000</v>
       </c>
       <c r="L3" t="n">
-        <v>1961000</v>
+        <v>150000</v>
       </c>
       <c r="M3" t="n">
-        <v>-242000</v>
+        <v>-10280000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>197897000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>197897000</v>
       </c>
       <c r="P3" t="n">
-        <v>2104000</v>
+        <v>-226387000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2104000</v>
+        <v>-226387000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1478000</v>
+        <v>-226387000</v>
       </c>
       <c r="S3" t="n">
-        <v>3582000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-17100000</v>
+        <v>-58000000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>157000</v>
+        <v>952000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2886000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3474000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-6360000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-6083000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1289000</v>
-      </c>
+        <v>-56968000</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-7372000</v>
+        <v>-56968000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-369000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-369000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5329000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-11002000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="n">
-        <v>-5329000</v>
+        <v>-11002000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2089000</v>
+        <v>-2247000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-271000</v>
+        <v>-511000</v>
       </c>
       <c r="AL3" t="n">
-        <v>18650000</v>
+        <v>11382000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1713000</v>
+        <v>613000</v>
       </c>
       <c r="AN3" t="n">
-        <v>21452000</v>
+        <v>33448000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-933000</v>
+        <v>4033000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-156000</v>
+        <v>-26754000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2457000</v>
+        <v>9374000</v>
       </c>
       <c r="AR3" t="n">
-        <v>555000</v>
+        <v>5873000</v>
       </c>
       <c r="AS3" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>476000</v>
+        <v>5873000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-8216000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>15429000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
       <c r="AW3" t="n">
-        <v>-2648000</v>
+        <v>385000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-11051000</v>
+        <v>-49540000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-13249000</v>
+        <v>-3609000</v>
       </c>
       <c r="C4" t="n">
-        <v>-226387000</v>
+        <v>-1478000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3582000</v>
       </c>
       <c r="E4" t="n">
-        <v>197897000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-11002000</v>
+        <v>-5698000</v>
       </c>
       <c r="G4" t="n">
+        <v>9150000</v>
+      </c>
+      <c r="H4" t="n">
         <v>24493000</v>
       </c>
-      <c r="H4" t="n">
-        <v>135567000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-2697000</v>
+        <v>-3195000</v>
       </c>
       <c r="J4" t="n">
-        <v>-108377000</v>
+        <v>-12148000</v>
       </c>
       <c r="K4" t="n">
-        <v>-48130000</v>
+        <v>2863000</v>
       </c>
       <c r="L4" t="n">
-        <v>150000</v>
+        <v>1961000</v>
       </c>
       <c r="M4" t="n">
-        <v>-10280000</v>
+        <v>-242000</v>
       </c>
       <c r="N4" t="n">
-        <v>197897000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>197897000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-226387000</v>
+        <v>2104000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-226387000</v>
+        <v>2104000</v>
       </c>
       <c r="R4" t="n">
-        <v>-226387000</v>
+        <v>-1478000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3582000</v>
       </c>
       <c r="T4" t="n">
-        <v>-58000000</v>
+        <v>-17100000</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>952000</v>
+        <v>157000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-2886000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3474000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-6360000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-56968000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>-6083000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1289000</v>
+      </c>
       <c r="AD4" t="n">
-        <v>-56968000</v>
+        <v>-7372000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-369000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-369000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-11002000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
+        <v>-5329000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-11002000</v>
+        <v>-5329000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2247000</v>
+        <v>2089000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-511000</v>
+        <v>-271000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11382000</v>
+        <v>18650000</v>
       </c>
       <c r="AM4" t="n">
-        <v>613000</v>
+        <v>-1713000</v>
       </c>
       <c r="AN4" t="n">
-        <v>33448000</v>
+        <v>21452000</v>
       </c>
       <c r="AO4" t="n">
-        <v>4033000</v>
+        <v>-933000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-26754000</v>
+        <v>-156000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9374000</v>
+        <v>-2457000</v>
       </c>
       <c r="AR4" t="n">
-        <v>5873000</v>
+        <v>555000</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5873000</v>
+        <v>476000</v>
       </c>
       <c r="AU4" t="n">
-        <v>15429000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
+        <v>-8216000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>385000</v>
+        <v>-2648000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-49540000</v>
+        <v>-11051000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>29156000</v>
+        <v>-65870000</v>
       </c>
       <c r="C5" t="n">
-        <v>-25000000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-11554000</v>
+        <v>-4227000</v>
       </c>
       <c r="G5" t="n">
-        <v>135567000</v>
+        <v>14699000</v>
       </c>
       <c r="H5" t="n">
-        <v>107051000</v>
+        <v>9150000</v>
       </c>
       <c r="I5" t="n">
-        <v>14583000</v>
+        <v>-460000</v>
       </c>
       <c r="J5" t="n">
-        <v>13933000</v>
+        <v>6009000</v>
       </c>
       <c r="K5" t="n">
-        <v>-56115000</v>
+        <v>25040000</v>
       </c>
       <c r="L5" t="n">
-        <v>8000</v>
+        <v>25998000</v>
       </c>
       <c r="M5" t="n">
-        <v>-26242000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>-40000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-25000000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-25000000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-25000000</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" t="n">
-        <v>29338000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>42612000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2584000</v>
+      </c>
       <c r="V5" t="n">
-        <v>729000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>10230000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>10230000</v>
-      </c>
+        <v>848000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4317000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4317000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>19730000</v>
+        <v>45897000</v>
       </c>
       <c r="AC5" t="n">
-        <v>19730000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+        <v>45897000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="n">
-        <v>-11354000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>200000</v>
-      </c>
+        <v>-4227000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-11554000</v>
+        <v>-4227000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40710000</v>
+        <v>-61643000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1280000</v>
+        <v>-880000</v>
       </c>
       <c r="AL5" t="n">
-        <v>38205000</v>
+        <v>-51176000</v>
       </c>
       <c r="AM5" t="n">
-        <v>11928000</v>
+        <v>130000</v>
       </c>
       <c r="AN5" t="n">
-        <v>9179000</v>
+        <v>99709000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-5073000</v>
+        <v>-72000</v>
       </c>
       <c r="AP5" t="n">
-        <v>22468000</v>
+        <v>-150943000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21672000</v>
+        <v>-715000</v>
       </c>
       <c r="AR5" t="n">
-        <v>13327000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>214000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
       <c r="AT5" t="n">
-        <v>13327000</v>
+        <v>214000</v>
       </c>
       <c r="AU5" t="n">
-        <v>12426000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-55000</v>
-      </c>
+        <v>23018000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>726000</v>
+        <v>-32136000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-52753000</v>
+        <v>-12776000</v>
       </c>
     </row>
   </sheetData>
@@ -3153,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL2"/>
+  <dimension ref="A1:EK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3179,690 +3179,685 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>website</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>industryKey</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>industryKey</t>
+          <t>industryDisp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>industryDisp</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sectorKey</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>sectorKey</t>
+          <t>sectorDisp</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>sectorDisp</t>
+          <t>longBusinessSummary</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>longBusinessSummary</t>
+          <t>fullTimeEmployees</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>fullTimeEmployees</t>
+          <t>companyOfficers</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>companyOfficers</t>
+          <t>compensationAsOfEpochDate</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>compensationAsOfEpochDate</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>open</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>exDividendDate</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>fiveYearAvgDividendYield</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>fiveYearAvgDividendYield</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
       <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3871,12 +3866,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hong Kong Plaza</t>
+          <t>Guangdong Finance Building</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Units 4214–15, 42nd Floor 188 Connaught Road West</t>
+          <t>12/F, 88 Connaught Road West</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3891,484 +3886,479 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>852 2909 6288</t>
+          <t>https://www.champion.hk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.champion.hk</t>
+          <t>Oil &amp; Gas Midstream</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>oil-gas-midstream</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Oil &amp; Gas Midstream</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>oil-gas-midstream</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Midstream</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>Champion Technology Holdings Limited, an investment holding company, engages in trading of gasoil and cultural products in the People's Republic of China. The company operates through five segments: Sales of Cultural Products, Technology: Smart City Solution Business, Technology: Renewable Energy, Trading of Gasoil and Related Business, and Strategic Investments. It sells cultural products, gasoil, and vessel charter; sells business solutions, including software and hardware for construction site and related businesses; and designs and sales renewable energy products and solutions; general system products; and provides systems and related software licensing services, as well as installation and maintenance services; leasing of system products; and IoT services, which include smart construction site and smart city. The company is involved in the research, development, and operation in gas fuel energy; money lending; property investment; software development activities, as well as provision engineering work services, as well as provides messaging services. Champion Technology Holdings Limited was incorporated in 1992 and is based in Hong Kong, Hong Kong.</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>45</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Ms. Man  Wong', 'age': 51, 'title': 'Executive Chairperson', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 3474000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Leung  Ng', 'age': 43, 'title': 'Company Secretary &amp; Financial Controller', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Seek Fan  Tong', 'age': 59, 'title': 'Vice President of Operations', 'yearBorn': 1966, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Man Yee  Mak', 'age': 57, 'title': 'Vice President of Administration &amp; Logistics', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yim Fan  Chiu', 'age': 54, 'title': 'Vice President of Compliance', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Terry John  Miller', 'age': 86, 'title': 'Consultant', 'yearBorn': 1939, 'fiscalYear': 2025, 'totalPay': 213000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Stephen Alan  Gentry', 'age': 69, 'title': 'CEO of Multitone Electronics PLC', 'yearBorn': 1956, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Frank  Rotthoff', 'age': 62, 'title': 'MD of German Operations &amp; Head of International Market', 'yearBorn': 1963, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hap Lee  King', 'age': 63, 'title': 'Executive Director', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Edward  Paterson', 'age': 53, 'title': 'Chief Executive Officer of Multitone UK', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="O2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="Q2" t="n">
+        <v>86400</v>
+      </c>
       <c r="R2" t="n">
-        <v>86400</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0.182</v>
       </c>
       <c r="T2" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="U2" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="V2" t="n">
         <v>0.188</v>
       </c>
       <c r="W2" t="n">
-        <v>0.19</v>
+        <v>0.182</v>
       </c>
       <c r="X2" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="Z2" t="n">
         <v>0.188</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.19</v>
+        <v>1394755200</v>
       </c>
       <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.532</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>365717</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>223880</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>223880</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>206351584</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>206351591</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>130.37003</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.9831233</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.19336</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>154207920</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.72940004</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>847675174</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1097614848</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.101210006</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1097614848</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.1123595</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1751241600</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1782777600</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-50455000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="BP2" t="n">
+        <v>1710806400</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-1.769</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.035897434</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.133697</v>
+      </c>
+      <c r="BV2" t="n">
         <v>1394755200</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.538</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>442453</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>593537</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>593537</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>208546816</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>206351591</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>130.37003</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.0148587</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.19256</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.194065</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>44369000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-87181000</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>22919000</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>69173000</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>29.444</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-0.20292999</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.67376</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>4711000</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-39872624</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-25532000</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-1.26033</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-1.21429</v>
+      </c>
+      <c r="CR2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>156177328</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.72940004</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>847675174</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1097614848</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.101210006</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1097614848</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>2.1348314</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1751241600</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1782777600</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-50455000</v>
-      </c>
-      <c r="BO2" t="n">
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>0092.HK</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1781682474</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_878108</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>CHAMPION TECH</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>3.296702</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Champion Technology Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1022031000000</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.0059999973</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0.182 - 0.188</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>365717</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.049999997</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.3623188</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>0.138 - 0.28</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.09200000999999999</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.32857147</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-3.5897434</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1740667719</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1740667719</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1710806400</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>2.258</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>-1.791</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>-0.10047847</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.133697</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1394755200</v>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CA2" t="n">
-        <v>44369000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>-87181000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>22919000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>69173000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>29.444</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>-0.20292999</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.67376</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>4711000</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-39872624</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>-25532000</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.06809999999999999</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>-1.26033</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-1.21429</v>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0092.HK</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>442453</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.37681162</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>0.138 - 0.28</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.3214286</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-10.047847</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1740667719</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1740667719</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.0025600046</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.013294581</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.004065007</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.020946626</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.0053600073</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.027720353</v>
+      </c>
+      <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1022031000000</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.002000004</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.188 - 0.19</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Champion Technology Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>CHAMPION TECH</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1780385233</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_878108</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.063832</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="EL2" t="inlineStr"/>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
